--- a/data/trans_orig/IP38E_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP38E_2023-Estudios-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10466</t>
+          <t>10933</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16851</t>
+          <t>17048</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13559</t>
+          <t>13592</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23415</t>
+          <t>23605</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26362</t>
+          <t>27129</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38198</t>
+          <t>38240</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,22%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5028</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14884</t>
+          <t>14851</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8881</t>
+          <t>8839</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20717</t>
+          <t>19950</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>42,37%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>114453</t>
+          <t>115664</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>133071</t>
+          <t>133376</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>146701</t>
+          <t>146638</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>159884</t>
+          <t>160343</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>267510</t>
+          <t>267160</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>289769</t>
+          <t>289781</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16086</t>
+          <t>15781</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34704</t>
+          <t>33493</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8197</t>
+          <t>7738</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21380</t>
+          <t>21443</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27469</t>
+          <t>27457</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>49728</t>
+          <t>50078</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37144</t>
+          <t>36879</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41061</t>
+          <t>41051</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64785</t>
+          <t>64983</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68769</t>
+          <t>68778</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>388</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>387</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>157227</t>
+          <t>157476</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>176039</t>
+          <t>176004</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>202410</t>
+          <t>202587</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>220819</t>
+          <t>220907</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>368685</t>
+          <t>368776</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>394305</t>
+          <t>392975</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,66%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19480</t>
+          <t>19515</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38292</t>
+          <t>38043</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17144</t>
+          <t>17056</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35553</t>
+          <t>35376</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39177</t>
+          <t>40507</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>64797</t>
+          <t>64706</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP38E_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP38E_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17730</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12934</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>21475</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>67,57%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>49,29%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>81,84%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>14314</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10933</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17048</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>76,81%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>58,67%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>91,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19305</t>
+          <t>15536</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13592</t>
+          <t>11433</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23605</t>
+          <t>18337</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>33619</t>
+          <t>33266</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27129</t>
+          <t>26834</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38240</t>
+          <t>38151</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>82,29%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8510</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4765</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13306</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>32,43%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>18,16%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>50,71%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4322</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1588</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7703</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>23,19%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8,52%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>41,33%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>1787</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14851</t>
+          <t>8691</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>13460</t>
+          <t>13098</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8839</t>
+          <t>8213</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19950</t>
+          <t>19530</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,12%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>26240</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>26240</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>26240</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>18636</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>18636</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>18636</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28443</t>
+          <t>20124</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28443</t>
+          <t>20124</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28443</t>
+          <t>20124</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>47079</t>
+          <t>46364</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>47079</t>
+          <t>46364</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47079</t>
+          <t>46364</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>143515</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>136264</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>149368</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>91,66%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>87,02%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>95,39%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>126206</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>115664</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>133376</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>84,61%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>77,54%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>89,42%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>154434</t>
+          <t>124409</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>146638</t>
+          <t>115448</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>160343</t>
+          <t>130783</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>280640</t>
+          <t>267925</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>267160</t>
+          <t>257618</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>289781</t>
+          <t>277212</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,81%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>13066</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7213</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>20317</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8,34%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>12,98%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>22951</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>15781</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>33493</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>15,39%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10,58%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>22,46%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13647</t>
+          <t>20956</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7738</t>
+          <t>14582</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21443</t>
+          <t>29917</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>36598</t>
+          <t>34021</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27457</t>
+          <t>24734</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>50078</t>
+          <t>44328</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156581</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156581</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156581</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>149157</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>149157</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>149157</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>168081</t>
+          <t>145365</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>168081</t>
+          <t>145365</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>168081</t>
+          <t>145365</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>317238</t>
+          <t>301946</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>317238</t>
+          <t>301946</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>317238</t>
+          <t>301946</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,74 +1406,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>36441</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>33487</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>37676</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>95,99%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>88,21%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>99,24%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>27726</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>27053</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>39897</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>36879</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>41051</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>96,28%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>88,99%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>99,06%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>91</t>
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>67622</t>
+          <t>63494</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64983</t>
+          <t>60358</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68778</t>
+          <t>64716</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -1519,107 +1519,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1524</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4478</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4,01%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>11,79%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1542</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>4560</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>11,01%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1543</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>302</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4660</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>37965</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>37965</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>37965</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>27726</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>27726</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>27726</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>41439</t>
+          <t>27053</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41439</t>
+          <t>27053</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41439</t>
+          <t>27053</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>69165</t>
+          <t>65018</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>69165</t>
+          <t>65018</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>69165</t>
+          <t>65018</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>197686</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>187060</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>203898</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>89,54%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>84,72%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>92,35%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>168247</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>157476</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>176004</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>86,05%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>80,54%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>90,02%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>213635</t>
+          <t>166998</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>202587</t>
+          <t>157881</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>220907</t>
+          <t>174815</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>381882</t>
+          <t>364684</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>368776</t>
+          <t>352379</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>392975</t>
+          <t>376801</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>91,16%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>23100</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16888</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>33726</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>10,46%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7,65%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>15,28%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>27272</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>19515</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>38043</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>13,95%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9,98%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>19,46%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>24328</t>
+          <t>25544</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17056</t>
+          <t>17727</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35376</t>
+          <t>34661</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>51600</t>
+          <t>48644</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>40507</t>
+          <t>36527</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>64706</t>
+          <t>60949</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>220786</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>220786</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>220786</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>283</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>195519</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>195519</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>195519</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>237963</t>
+          <t>192542</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>237963</t>
+          <t>192542</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>237963</t>
+          <t>192542</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>433482</t>
+          <t>413328</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>433482</t>
+          <t>413328</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>433482</t>
+          <t>413328</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
